--- a/audio/Memorial Hall/2026-09-28 The Carole King and James Taylor Story/The Carole King and James Taylor Story - Input List.xlsx
+++ b/audio/Memorial Hall/2026-09-28 The Carole King and James Taylor Story/The Carole King and James Taylor Story - Input List.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Memorial Hall · 2026-09-28 + 2026-09-30 · Rev 1.0 Deep Think</t>
+          <t>Memorial Hall · 2026-09-28 · Rev 1.0 Deep Think</t>
         </is>
       </c>
     </row>
